--- a/new-stats/shimizu-s-pulse.xlsx
+++ b/new-stats/shimizu-s-pulse.xlsx
@@ -975,22 +975,62 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mito Hollyhock</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Shimizu</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>

--- a/new-stats/shimizu-s-pulse.xlsx
+++ b/new-stats/shimizu-s-pulse.xlsx
@@ -1033,22 +1033,62 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Shimizu</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>G-Osaka</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>

--- a/new-stats/shimizu-s-pulse.xlsx
+++ b/new-stats/shimizu-s-pulse.xlsx
@@ -1091,40 +1091,120 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Shimizu</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hiroshima</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Shimizu</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="n">
+        <v>16</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
